--- a/docs/samples/lumenvale-org-documentation.xlsx
+++ b/docs/samples/lumenvale-org-documentation.xlsx
@@ -21,20 +21,25 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Login Restrictions" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Record Types" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layouts" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unused Layouts" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Record Pages" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buttons and Links" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="List Views" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Field Sets" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apps" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flows" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Approval Processes" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apex Classes" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apex Triggers" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visualforce" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lightning Components" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Static Resources" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Custom Permissions" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields on Layouts" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unused Layouts" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Record Pages" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buttons and Links" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="List Views" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Field Sets" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apps" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flows" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flow Elements" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flow Fields" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Approval Processes" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Approval Steps" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apex Classes" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apex Triggers" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visualforce" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lightning Components" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Static Resources" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Custom Permissions" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Data Sources" sheetId="33" state="visible" r:id="rId33"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Objects'!$A$1:$L$30</definedName>
@@ -48,22 +53,27 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Assignments'!$A$1:$D$952</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Profile Users'!$A$1:$D$401</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Login Restrictions'!$A$1:$D$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Record Types'!$A$1:$F$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Record Types'!$A$1:$G$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Layouts'!$A$1:$E$67</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Unused Layouts'!$A$1:$C$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Record Pages'!$A$1:$D$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Buttons and Links'!$A$1:$F$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'List Views'!$A$1:$C$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Field Sets'!$A$1:$C$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Apps'!$A$1:$F$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'Flows'!$A$1:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Approval Processes'!$A$1:$F$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Apex Classes'!$A$1:$M$82</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'Apex Triggers'!$A$1:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'Visualforce'!$A$1:$H$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'Lightning Components'!$A$1:$G$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'Static Resources'!$A$1:$F$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'Custom Permissions'!$A$1:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Fields on Layouts'!$A$1:$I$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Unused Layouts'!$A$1:$C$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Record Pages'!$A$1:$D$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Buttons and Links'!$A$1:$F$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'List Views'!$A$1:$C$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Field Sets'!$A$1:$C$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'Apps'!$A$1:$F$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Flows'!$A$1:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Flow Elements'!$A$1:$Q$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'Flow Fields'!$A$1:$G$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'Approval Processes'!$A$1:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'Approval Steps'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'Apex Classes'!$A$1:$M$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'Apex Triggers'!$A$1:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'Visualforce'!$A$1:$H$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'Lightning Components'!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'Static Resources'!$A$1:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="31" hidden="1">'Custom Permissions'!$A$1:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="32" hidden="1">'External Data Sources'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -488,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -527,7 +537,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 21:16 UTC</t>
+          <t>2026-10-20 02:52 UTC</t>
         </is>
       </c>
     </row>
@@ -551,7 +561,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 21:16 UTC</t>
+          <t>2026-10-20 02:52 UTC</t>
         </is>
       </c>
     </row>
@@ -563,7 +573,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 21:16 UTC</t>
+          <t>2026-10-20 02:52 UTC</t>
         </is>
       </c>
     </row>
@@ -623,29 +633,41 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 21:16 UTC</t>
+          <t>2026-10-20 02:52 UTC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Not included yet</t>
+          <t>Fields on layouts</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Flow detail (elements, and the objects and fields each flow uses), which fields sit on which layout, custom metadata records, and approval process steps.</t>
+          <t>Who gets a layout comes from the profile layout assignments; a field on it shows only for those who can read the field, which the last column counts.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
+          <t>Not included yet</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Custom metadata records, and approval process entry criteria and approvers (they need the Metadata API, which isn't confirmed to work with Newton's permissions).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>2 fields aren't visible to the integration user (field-level security), so the describe left them out: their type comes from FieldDefinition; encryption, formula text and picklist values aren't known for them.</t>
         </is>
@@ -30593,7 +30615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -30602,6 +30624,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30635,6 +30658,11 @@
           <t>Default for profiles</t>
         </is>
       </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Available through permission sets</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -30663,6 +30691,11 @@
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Case Escalation (in Support Lead Bundle)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -30695,6 +30728,7 @@
           <t>Finance Analyst, Finance Director, Marketing Manager, Marketing User, Sales Director, Sales Manager, Sales Rep, Standard User, Support Agent, Support Manager, System Administrator</t>
         </is>
       </c>
+      <c r="G3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -30727,6 +30761,7 @@
           <t>Finance Analyst, Finance Director, Marketing Manager, Marketing User, Sales Director, Sales Manager, Sales Rep, Standard User, Support Agent, Support Manager, System Administrator</t>
         </is>
       </c>
+      <c r="G4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -30755,6 +30790,11 @@
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Opportunity Approvals (in Sales Manager Bundle)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -30783,9 +30823,10 @@
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F6"/>
+  <autoFilter ref="A1:G6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -32495,6 +32536,2100 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Layout</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Behavior</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Layout assigned to profiles</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Active users who get the layout</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Of them, can read the field</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Account - Legacy Layout</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Account Information</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Not assigned</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>OwnerId</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Owner ID</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Account - Legacy Layout</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Account Information</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Not assigned</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Account - Legacy Layout</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Account Information</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Not assigned</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Account - Sales Layout</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Account Information</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director, Sales Manager, Sales Rep</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>153</v>
+      </c>
+      <c r="I5" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>OwnerId</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Owner ID</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Account - Sales Layout</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Account Information</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director, Sales Manager, Sales Rep</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>153</v>
+      </c>
+      <c r="I6" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Account - Sales Layout</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Account Information</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director, Sales Manager, Sales Rep</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>153</v>
+      </c>
+      <c r="I7" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Account - Sales Layout</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Account Information</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director, Sales Manager, Sales Rep</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>153</v>
+      </c>
+      <c r="I8" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AnnualRevenue</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AnnualRevenue</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Account - Sales Layout</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director, Sales Manager, Sales Rep</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>153</v>
+      </c>
+      <c r="I9" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tax_ID__c</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Tax ID</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Account - Sales Layout</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Readonly</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director, Sales Manager, Sales Rep</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>153</v>
+      </c>
+      <c r="I10" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Account Layout</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Account Information</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Finance Analyst, Finance Director, Marketing Manager, Marketing User, Standard User, Support Agent, Support Manager, System Administrator</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>247</v>
+      </c>
+      <c r="I11" t="n">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>OwnerId</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Owner ID</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Account Layout</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Account Information</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Finance Analyst, Finance Director, Marketing Manager, Marketing User, Standard User, Support Agent, Support Manager, System Administrator</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>247</v>
+      </c>
+      <c r="I12" t="n">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Account Layout</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Account Information</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Finance Analyst, Finance Director, Marketing Manager, Marketing User, Standard User, Support Agent, Support Manager, System Administrator</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>247</v>
+      </c>
+      <c r="I13" t="n">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Account Layout</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Account Information</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Finance Analyst, Finance Director, Marketing Manager, Marketing User, Standard User, Support Agent, Support Manager, System Administrator</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>247</v>
+      </c>
+      <c r="I14" t="n">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AnnualRevenue</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AnnualRevenue</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Account Layout</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Finance Analyst, Finance Director, Marketing Manager, Marketing User, Standard User, Support Agent, Support Manager, System Administrator</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>247</v>
+      </c>
+      <c r="I15" t="n">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CaseNumber</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CaseNumber</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Case - Billing Layout</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Case Information</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Readonly</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Support Agent, Support Manager</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>38</v>
+      </c>
+      <c r="I16" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>OwnerId</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Owner ID</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Case - Billing Layout</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Case Information</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Support Agent, Support Manager</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>38</v>
+      </c>
+      <c r="I17" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Case - Billing Layout</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Case Information</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Support Agent, Support Manager</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>38</v>
+      </c>
+      <c r="I18" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Case - Billing Layout</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Case Information</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Support Agent, Support Manager</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>38</v>
+      </c>
+      <c r="I19" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CaseNumber</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CaseNumber</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Case - Old Support Layout</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Case Information</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Readonly</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Not assigned</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>OwnerId</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Owner ID</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Case - Old Support Layout</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Case Information</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Not assigned</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Case - Old Support Layout</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Case Information</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Not assigned</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CaseNumber</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CaseNumber</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Case Layout</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Case Information</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Readonly</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Finance Analyst, Finance Director, Marketing Manager, Marketing User, Sales Director, Sales Manager, Sales Rep, Standard User, Support Agent, Support Manager, System Administrator</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>400</v>
+      </c>
+      <c r="I23" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>OwnerId</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Owner ID</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Case Layout</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Case Information</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Finance Analyst, Finance Director, Marketing Manager, Marketing User, Sales Director, Sales Manager, Sales Rep, Standard User, Support Agent, Support Manager, System Administrator</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>400</v>
+      </c>
+      <c r="I24" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Case Layout</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Case Information</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Finance Analyst, Finance Director, Marketing Manager, Marketing User, Sales Director, Sales Manager, Sales Rep, Standard User, Support Agent, Support Manager, System Administrator</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>400</v>
+      </c>
+      <c r="I25" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Case Layout</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Case Information</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Finance Analyst, Finance Director, Marketing Manager, Marketing User, Sales Director, Sales Manager, Sales Rep, Standard User, Support Agent, Support Manager, System Administrator</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>400</v>
+      </c>
+      <c r="I26" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Customer_Sentiment__c</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Customer Sentiment</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Case Layout</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Case Information</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Readonly</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Finance Analyst, Finance Director, Marketing Manager, Marketing User, Sales Director, Sales Manager, Sales Rep, Standard User, Support Agent, Support Manager, System Administrator</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>400</v>
+      </c>
+      <c r="I27" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Opportunity - Partner Layout</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Opportunity Information</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director, Sales Manager, Sales Rep</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>153</v>
+      </c>
+      <c r="I28" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>OwnerId</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Owner ID</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Opportunity - Partner Layout</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Opportunity Information</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director, Sales Manager, Sales Rep</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>153</v>
+      </c>
+      <c r="I29" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>StageName</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>StageName</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Opportunity - Partner Layout</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Opportunity Information</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director, Sales Manager, Sales Rep</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>153</v>
+      </c>
+      <c r="I30" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Opportunity - Partner Layout</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Opportunity Information</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director, Sales Manager, Sales Rep</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>153</v>
+      </c>
+      <c r="I31" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Discount_Percent__c</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Discount Percent</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Opportunity - Partner Layout</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Pricing</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director, Sales Manager, Sales Rep</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>153</v>
+      </c>
+      <c r="I32" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Opportunity - Renewal Layout</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Opportunity Information</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director, Sales Manager, Sales Rep</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>153</v>
+      </c>
+      <c r="I33" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>OwnerId</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Owner ID</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Opportunity - Renewal Layout</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Opportunity Information</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director, Sales Manager, Sales Rep</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>153</v>
+      </c>
+      <c r="I34" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>StageName</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>StageName</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Opportunity - Renewal Layout</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Opportunity Information</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director, Sales Manager, Sales Rep</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>153</v>
+      </c>
+      <c r="I35" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Opportunity - Renewal Layout</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Opportunity Information</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director, Sales Manager, Sales Rep</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>153</v>
+      </c>
+      <c r="I36" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Discount_Percent__c</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Discount Percent</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Opportunity - Renewal Layout</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Pricing</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director, Sales Manager, Sales Rep</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>153</v>
+      </c>
+      <c r="I37" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Opportunity - Sales Manager Layout</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Opportunity Information</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director, Sales Manager</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>84</v>
+      </c>
+      <c r="I38" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>OwnerId</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Owner ID</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Opportunity - Sales Manager Layout</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Opportunity Information</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director, Sales Manager</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>84</v>
+      </c>
+      <c r="I39" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>StageName</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>StageName</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Opportunity - Sales Manager Layout</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Opportunity Information</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director, Sales Manager</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>84</v>
+      </c>
+      <c r="I40" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Opportunity - Sales Manager Layout</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Opportunity Information</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director, Sales Manager</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>84</v>
+      </c>
+      <c r="I41" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Discount_Percent__c</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Discount Percent</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Opportunity - Sales Manager Layout</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Pricing</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director, Sales Manager</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>84</v>
+      </c>
+      <c r="I42" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CreatedDate</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Opportunity - Sales Manager Layout</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Pricing</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Readonly</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director, Sales Manager</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>84</v>
+      </c>
+      <c r="I43" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Opportunity Layout</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Opportunity Information</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Finance Analyst, Finance Director, Marketing Manager, Marketing User, Sales Rep, Standard User, Support Agent, Support Manager, System Administrator</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>316</v>
+      </c>
+      <c r="I44" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>OwnerId</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Owner ID</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Opportunity Layout</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Opportunity Information</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Finance Analyst, Finance Director, Marketing Manager, Marketing User, Sales Rep, Standard User, Support Agent, Support Manager, System Administrator</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>316</v>
+      </c>
+      <c r="I45" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>StageName</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>StageName</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Opportunity Layout</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Opportunity Information</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Finance Analyst, Finance Director, Marketing Manager, Marketing User, Sales Rep, Standard User, Support Agent, Support Manager, System Administrator</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>316</v>
+      </c>
+      <c r="I46" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Opportunity Layout</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Opportunity Information</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Finance Analyst, Finance Director, Marketing Manager, Marketing User, Sales Rep, Standard User, Support Agent, Support Manager, System Administrator</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>316</v>
+      </c>
+      <c r="I47" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Discount_Percent__c</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Discount Percent</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Opportunity Layout</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Pricing</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Finance Analyst, Finance Director, Marketing Manager, Marketing User, Sales Rep, Standard User, Support Agent, Support Manager, System Administrator</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>316</v>
+      </c>
+      <c r="I48" t="n">
+        <v>237</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I48"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -32560,7 +34695,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -32735,7 +34870,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -32950,7 +35085,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -33204,77 +35339,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:C14"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Field set</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Employee_Directory</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Employee Directory</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Fields shown in the HR portal directory.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Invoice_Summary</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Invoice Summary</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Fields for the invoice summary component.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:C3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -34662,6 +36726,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Field set</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Employee_Directory</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Employee Directory</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Fields shown in the HR portal directory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Invoice_Summary</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Invoice Summary</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Fields for the invoice summary component.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -34841,7 +36976,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -35535,7 +37670,3550 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Flow</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>API name</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Start object</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Runs when</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Variables</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Formulas</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Screens</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Decisions</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Assignments</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>Loops</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Get records</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Create records</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Update records</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Subflows</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Actions</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Subflows called</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Actions called</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Account Owner Notification</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Account_Owner_Notify</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Account_Owner_Changed (emailAlert)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Calculate Commission</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Calculate_Commission</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Case Assignment</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Case_Assignment_Rules</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Created</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Case Triage</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Case_Triage</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Close Stale Cases</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Close_Stale_Cases</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Discount Approval Request</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Discount_Approval_Request</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>submit (submit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Lead Qualification</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Lead_Qualification</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Update_Territory</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Log a Customer Call</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Log_Customer_Call</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>New Opportunity Wizard</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>New_Opportunity_Wizard</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Nightly Renewal Reminders</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Nightly_Renewal_Reminders</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Opportunity Stage Sync</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Opportunity_Stage_Sync</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Order Event Handler</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Order_Event_Handler</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PlatformEvent</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Quote Builder</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Quote_Builder</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Refund Exception</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Refund_Exception</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Update Territory</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Update_Territory</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q16"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G79"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Flow</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Operation</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Used as</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Account Owner Notification</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Trigger condition</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>OwnerId</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Calculate Commission</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Get Closed Opportunities</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Calculate Commission</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Get Closed Opportunities</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CloseDate</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Calculate Commission</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Get Closed Opportunities</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>OwnerId</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Calculate Commission</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Get Closed Opportunities</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>StageName</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Case Assignment</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Set Owner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>OwnerId</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Written</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Case Assignment</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Set Owner</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Written</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Case Triage</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Get Case</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Case Triage</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Get Case</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Product_Area__c</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Case Triage</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Get Case</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Case Triage</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Get Case</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Case Triage</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Get Case</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Case Triage</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Set Priority</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Customer_Sentiment__c</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Written</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Case Triage</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Set Priority</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Written</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Case Triage</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Set Priority</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Close Stale Cases</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Get Stale Cases</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>LastModifiedDate</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Close Stale Cases</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Get Stale Cases</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Close Stale Cases</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Get Stale Cases</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Close Stale Cases</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Close Cases</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Written</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Discount Approval Request</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Get Opportunity</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Discount Approval Request</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Get Opportunity</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Discount_Percent__c</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Discount Approval Request</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Get Opportunity</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>StageName</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Discount Approval Request</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Get Opportunity</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Discount Approval Request</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Save Discount</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Discount_Percent__c</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Written</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Discount Approval Request</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Save Discount</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>NextStep</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Written</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Discount Approval Request</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Save Discount</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Lead Qualification</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Get Lead</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Lead Qualification</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Get Lead</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Lead Qualification</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Get Lead</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>LeadSource</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Lead Qualification</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Get Lead</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Lead_Score__c</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Lead Qualification</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Get Lead</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Lead Qualification</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Update Score</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Lead_Score__c</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Written</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Lead Qualification</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Update Score</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Log a Customer Call</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Create Call</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Written</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Log a Customer Call</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Create Call</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>WhatId</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Written</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Log a Customer Call</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Create Call</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>WhoId</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Written</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>New Opportunity Wizard</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Get Account</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>New Opportunity Wizard</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Get Account</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>New Opportunity Wizard</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Get Account</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Segment__c</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>New Opportunity Wizard</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Get Account</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>New Opportunity Wizard</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Create Opportunity</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AccountId</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Written</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>New Opportunity Wizard</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Create Opportunity</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Written</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>New Opportunity Wizard</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Create Opportunity</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>CloseDate</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Written</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>New Opportunity Wizard</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Create Opportunity</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Written</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>New Opportunity Wizard</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Create Opportunity</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>StageName</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Written</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Nightly Renewal Reminders</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Get Expiring Contracts</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AccountId</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Nightly Renewal Reminders</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Get Expiring Contracts</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ContractTerm</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Nightly Renewal Reminders</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Get Expiring Contracts</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>OwnerId</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Nightly Renewal Reminders</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Get Expiring Contracts</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>ContractTerm</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Nightly Renewal Reminders</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Create Reminder Tasks</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Whole record from the variable ReminderTasks</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Opportunity Stage Sync</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Trigger condition</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>StageName</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Opportunity Stage Sync</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Get Account</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Opportunity Stage Sync</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Get Account</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Opportunity Stage Sync</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Update Account Rating</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Written</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Opportunity Stage Sync</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Update Account Rating</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Order Event Handler</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Get Order</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Order</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Order Event Handler</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Get Order</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Order</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>TotalAmount</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Order Event Handler</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Get Order</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Order</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>OrderNumber</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Order Event Handler</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Mark Fulfilled</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Order</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Written</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Order Event Handler</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Mark Fulfilled</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Order</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Quote Builder</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Get Opportunity</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Quote Builder</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Get Opportunity</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Discounted_Amount__c</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Quote Builder</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Get Opportunity</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Quote Builder</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Get Opportunity</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Quote Builder</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Get Account</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Quote Builder</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Get Account</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Segment__c</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Quote Builder</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Get Account</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Quote Builder</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Create Quote</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Written</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Quote Builder</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Create Quote</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>OpportunityId</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Written</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Refund Exception</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Get Invoice</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Invoice__c</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Account__c</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Refund Exception</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Get Invoice</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Invoice__c</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Amount__c</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Refund Exception</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Get Invoice</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Invoice__c</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Days_Overdue__c</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Refund Exception</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Get Invoice</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Invoice__c</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Refund Exception</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Log Refund Task</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>OwnerId</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Written</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Refund Exception</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Log Refund Task</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Written</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Refund Exception</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Log Refund Task</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>WhatId</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Written</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Update Territory</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Set Region</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Region__c</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Written</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Update Territory</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Set Region</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G79"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -35686,7 +41364,212 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Approval process</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>API name</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Entry criteria and approvers</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Discount over 20%</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Sales Director Review</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sales_Director_Review</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>The account's sales director approves.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Not read: they need the Metadata API, which isn't confirmed to work with Newton's permissions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Discount over 20%</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Finance Review over 40%</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Finance_Review_Over_40</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Discounts over 40% also go to finance.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Not read: they need the Metadata API, which isn't confirmed to work with Newton's permissions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Invoice over 50K</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Invoice__c</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Finance Director Approval</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Finance_Director_Approval</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Not read: they need the Metadata API, which isn't confirmed to work with Newton's permissions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Legacy Contract Approval</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Legal Review</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Legal_Review</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Replaced by a flow in 2025.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Not read: they need the Metadata API, which isn't confirmed to work with Newton's permissions.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -39502,7 +45385,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -40043,7 +45926,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -40239,568 +46122,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:H5"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Namespace</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>API version</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Exposed in App Builder</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Aura</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>legacyCaseSidebar</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Legacy Case Sidebar</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="n">
-        <v>44</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Case console sidebar (Aura).</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Aura</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>quickQuoteAction</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Quick Quote</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="n">
-        <v>50</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Quick action to start a quote.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Lightning web component</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>approvalBanner</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Approval Banner</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="n">
-        <v>62</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Shows pending approvals.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Lightning web component</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>caseTimeline</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Case Timeline</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="n">
-        <v>61</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Used inside other components.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Lightning web component</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>invoiceSummary</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Invoice Summary</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="n">
-        <v>62</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Invoice totals on the account page.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Lightning web component</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>salaryBandBadge</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Salary Band Badge</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="n">
-        <v>64</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Shows an employee's salary band.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Lightning web component</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>treasuryBalanceCard</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Treasury Balance Card</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="n">
-        <v>60</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Treasury balances.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G8"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Namespace</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Content type</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Size (bytes)</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Cache control</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>invoice_styles</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>text/css</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="n">
-        <v>5120</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Private</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Styles for InvoicePrint.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>jquery_3_6</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>application/javascript</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="n">
-        <v>89476</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>jQuery for the legacy treasury page.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>legacy_charts</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>application/zip</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>412907</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Private</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Charting library for the legacy treasury page.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>lumenvale_logo</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>image/png</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>18342</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Logo for PDFs.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:F5"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Custom permission</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Namespace</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Access granted by</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Active users granted it</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Approve_Large_Discounts</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Approve Large Discounts</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Approves discounts over 20%.</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Discount Approvals (in Sales Manager Bundle), Sales Director (Profile)</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Bypass_Validation</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Bypass Validation</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Skips validation rules that check it, for data loads.</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Legacy Integration Admin, System Administrator (Profile)</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>View_Salary_Bands</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>View Salary Bands</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Shows salary bands in the salary band badge.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Compensation Admin</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:F4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -55470,6 +60791,675 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:P261"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Namespace</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>API version</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Exposed in App Builder</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Aura</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>legacyCaseSidebar</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Legacy Case Sidebar</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>44</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Case console sidebar (Aura).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aura</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>quickQuoteAction</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Quick Quote</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Quick action to start a quote.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Lightning web component</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>approvalBanner</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Approval Banner</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>62</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Shows pending approvals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lightning web component</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>caseTimeline</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Case Timeline</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>61</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Used inside other components.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Lightning web component</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>invoiceSummary</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Invoice Summary</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>62</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Invoice totals on the account page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Lightning web component</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>salaryBandBadge</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Salary Band Badge</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>64</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Shows an employee's salary band.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Lightning web component</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>treasuryBalanceCard</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Treasury Balance Card</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>60</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Treasury balances.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G8"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Namespace</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Content type</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Size (bytes)</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Cache control</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>invoice_styles</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>text/css</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>5120</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Styles for InvoicePrint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>jquery_3_6</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>application/javascript</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>89476</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>jQuery for the legacy treasury page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>legacy_charts</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>application/zip</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>412907</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Charting library for the legacy treasury page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>lumenvale_logo</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>image/png</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>18342</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Logo for PDFs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Custom permission</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Namespace</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Access granted by</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Active users granted it</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Approve_Large_Discounts</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Approve Large Discounts</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Approves discounts over 20%.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Discount Approvals (in Sales Manager Bundle), Sales Director (Profile)</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bypass_Validation</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bypass Validation</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Skips validation rules that check it, for data loads.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Legacy Integration Admin, System Administrator (Profile)</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>View_Salary_Bands</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>View Salary Bands</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Shows salary bands in the salary band badge.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Compensation Admin</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>External data source</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Namespace</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Access granted by</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Active users granted it</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ERP_Orders</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ERP Orders</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>OData4</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Finance Director (Profile), Finance Reporting (in Finance Ops Bundle), System Administrator (Profile)</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Legacy_Archive</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Legacy Archive</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>OData</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Legacy Integration Admin</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/samples/lumenvale-org-documentation.xlsx
+++ b/docs/samples/lumenvale-org-documentation.xlsx
@@ -40,6 +40,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Static Resources" sheetId="31" state="visible" r:id="rId31"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Custom Permissions" sheetId="32" state="visible" r:id="rId32"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Data Sources" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Custom Metadata Types" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Custom Metadata Records" sheetId="35" state="visible" r:id="rId35"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Objects'!$A$1:$L$30</definedName>
@@ -74,6 +76,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'Static Resources'!$A$1:$F$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="31" hidden="1">'Custom Permissions'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="32" hidden="1">'External Data Sources'!$A$1:$F$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="33" hidden="1">'Custom Metadata Types'!$A$1:$C$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="34" hidden="1">'Custom Metadata Records'!$A$1:$F$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,7 +88,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -94,6 +98,9 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -121,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -133,6 +140,7 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -498,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -537,7 +545,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 02:52 UTC</t>
+          <t>2026-10-20 02:59 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +569,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 02:52 UTC</t>
+          <t>2026-10-20 02:59 UTC</t>
         </is>
       </c>
     </row>
@@ -573,7 +581,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 02:52 UTC</t>
+          <t>2026-10-20 02:59 UTC</t>
         </is>
       </c>
     </row>
@@ -633,7 +641,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 02:52 UTC</t>
+          <t>2026-10-20 02:59 UTC</t>
         </is>
       </c>
     </row>
@@ -652,22 +660,34 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Not included yet</t>
+          <t>Custom metadata</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Custom metadata records, and approval process entry criteria and approvers (they need the Metadata API, which isn't confirmed to work with Newton's permissions).</t>
+          <t>Records are read only for the types an admin turned on for this org (Privacy &amp; Data); the Custom Metadata Types sheet says which.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
+          <t>Not included yet</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Approval process entry criteria and approvers (they need the Metadata API, which isn't confirmed to work with Newton's permissions).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>2 fields aren't visible to the integration user (field-level security), so the describe left them out: their type comes from FieldDefinition; encryption, formula text and picklist values aren't known for them.</t>
         </is>
@@ -61460,6 +61480,173 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Records</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Discount_Threshold__mdt</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Discount Threshold</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Not read: an admin can turn this type on in Privacy &amp; Data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Feature_Switch__mdt</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Feature Switch</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Not read: an admin can turn this type on in Privacy &amp; Data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Integration_Endpoint__mdt</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Integration Endpoint</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Not read: an admin can turn this type on in Privacy &amp; Data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Region_Mapping__mdt</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Region Mapping</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Not read: an admin can turn this type on in Privacy &amp; Data.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Namespace</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>No custom metadata records: no type is turned on, or none was read yet.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/samples/lumenvale-org-documentation.xlsx
+++ b/docs/samples/lumenvale-org-documentation.xlsx
@@ -43,6 +43,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Custom Metadata Types" sheetId="34" state="visible" r:id="rId34"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Custom Metadata Records" sheetId="35" state="visible" r:id="rId35"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cleanup Candidates" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change History" sheetId="37" state="visible" r:id="rId37"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Objects'!$A$1:$L$30</definedName>
@@ -80,6 +81,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="33" hidden="1">'Custom Metadata Types'!$A$1:$C$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="34" hidden="1">'Custom Metadata Records'!$A$1:$F$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="35" hidden="1">'Cleanup Candidates'!$A$1:$I$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="36" hidden="1">'Change History'!$A$1:$H$61</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -130,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -143,6 +145,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -508,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -547,7 +550,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 03:36 UTC</t>
+          <t>2026-10-20 03:43 UTC</t>
         </is>
       </c>
     </row>
@@ -571,7 +574,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 03:36 UTC</t>
+          <t>2026-10-20 03:43 UTC</t>
         </is>
       </c>
     </row>
@@ -583,7 +586,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 03:36 UTC</t>
+          <t>2026-10-20 03:43 UTC</t>
         </is>
       </c>
     </row>
@@ -643,7 +646,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 03:36 UTC</t>
+          <t>2026-10-20 03:43 UTC</t>
         </is>
       </c>
     </row>
@@ -692,6 +695,18 @@
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>2 fields aren't visible to the integration user (field-level security), so the describe left them out: their type comes from FieldDefinition; encryption, formula text and picklist values aren't known for them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Change history</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>60 Setup Audit Trail events from 2026-09-20 to 2026-10-20, from 1 Change-Risk Radar pull. Salesforce keeps the audit trail for at least 180 days; Newton keeps what it pulled, under its retention settings, so older pulls extend it. The trail doesn't record a field's old and new values.</t>
         </is>
       </c>
     </row>
@@ -64894,6 +64909,2237 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I79"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>When (UTC)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Changed by</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>On behalf of</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Blast radius</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-20 00:02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Manage Users</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>changedUserEmail</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Changed email for user Priya Raman</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Idris Castellan</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:15</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Manage Permission Sets</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PermSetAssign</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Permission set Quote Manager: assigned to user Tobias Lindqvist</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Callum Yarrow</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-18 03:53</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Package Manager</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>uninstalledPackage</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Uninstalled package Legacy Survey Tool, permanently deleted its data</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Odette Fennimore</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-17 17:56</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Company Information</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>changedOrgTimeZone</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Changed default time zone</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Nikhil Pemberton</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-16 23:27</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Custom Metadata</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>changedCustomMetadataRecord</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Changed Discount Threshold record Strategic</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Odette Fennimore</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-16 17:13</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Field-Level Security</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>changedFieldSecurity</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Changed field-level security for Compensation Salary Band</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Nikhil Pemberton</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-16 13:52</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Custom Metadata</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>changedCustomMetadataRecord</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Changed Discount Threshold record Strategic</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Odette Fennimore</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-15 15:52</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Manage Users</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>changedUserEmail</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Changed email for user Elin Sorensen</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Odette Fennimore</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-14 19:50</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Flows</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>activatedinteractiondefversion</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Activated flow version Case Triage, version 4</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ayla Zielinski</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-13 19:43</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Manage Profiles</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>profileFlsChanged</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Changed profile Sales Rep: field-level security for Account Tax ID</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Callum Yarrow</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:27</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Manage Users</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>deactivateduser</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Deactivated user Tobias Lindqvist</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Odette Fennimore</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-12 18:38</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Custom Objects</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>changedCFLength</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Changed field length for Invoice PO Number from 20 to 30</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Marlow Sallow</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-12 17:21</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Flows</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>activatedinteractiondefversion</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Activated flow version Case Triage, version 4</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Callum Yarrow</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-11 19:02</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Custom Objects</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>changedCFLength</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Changed field length for Invoice PO Number from 20 to 30</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Odette Fennimore</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-10 22:03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Flows</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>deactivatedinteractiondefversion</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Deactivated flow version Legacy Fax Sync, version 3</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Ayla Zielinski</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-10 21:12</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Customize Accounts</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>changedPicklistValue</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Changed Account Industry picklist value Biotech to Life Sciences</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Nikhil Pemberton</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-07 22:18</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Custom Metadata</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>changedCustomMetadataRecord</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Changed Discount Threshold record Strategic</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Callum Yarrow</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-07 19:44</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Manage Permission Sets</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PermSetUnassign</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Permission set Lead Conversion: unassigned from user Priya Raman</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Callum Yarrow</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:48</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Validation Rules</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>newValidationRule</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Created validation rule Old_Score_Range on Account</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Idris Castellan</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:45</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Manage Users</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>createduser</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Created new user Noor Whitlock</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Marlow Sallow</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-06 21:00</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Customize Opportunities</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>createdCFRecordTypeLayout</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Changed page layout assignment for Opportunity Renewal</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Callum Yarrow</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-06 19:51</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Customize Opportunities</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>createdCFRecordTypeLayout</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Changed page layout assignment for Opportunity Renewal</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Odette Fennimore</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-06 15:38</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Manage Users</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>changedUserEmail</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Changed email for user Noor Whitlock</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Idris Castellan</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-05 23:14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Manage Users</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>resetPassword</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Reset password for Priya Raman</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Idris Castellan</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-05 18:12</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Flows</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>activatedinteractiondefversion</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Activated flow version Case Triage, version 4</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Nikhil Pemberton</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-04 23:53</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Custom Objects</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>changedCFLength</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Changed field length for Invoice PO Number from 20 to 30</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Nikhil Pemberton</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-04 21:11</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Manage Permission Sets</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PermSetAssign</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Permission set Discount Approvals: assigned to user Jun Jovanovic</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Freya Marchetti</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-04 21:07</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Manage Permission Sets</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PermSetAssign</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Permission set Discount Approvals: assigned to user Noor Whitlock</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Freya Marchetti</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-04 21:03</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Manage Permission Sets</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PermSetAssign</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Permission set Discount Approvals: assigned to user Elin Sorensen</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Freya Marchetti</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-04 20:59</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Manage Permission Sets</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PermSetAssign</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Permission set Discount Approvals: assigned to user Mateo Varga</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Freya Marchetti</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-04 20:55</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Manage Permission Sets</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PermSetAssign</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Permission set Discount Approvals: assigned to user Priya Raman</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Freya Marchetti</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-04 20:51</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Manage Permission Sets</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PermSetAssign</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Permission set Discount Approvals: assigned to user Tobias Lindqvist</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Freya Marchetti</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-04 20:51</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Custom Objects</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>changedCFLength</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Changed field length for Invoice PO Number from 20 to 30</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Nikhil Pemberton</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-04 20:47</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Manage Permission Sets</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>PermSetAssign</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Permission set Discount Approvals: assigned to user Jun Jovanovic</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Freya Marchetti</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-04 20:43</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Manage Permission Sets</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>PermSetAssign</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Permission set Discount Approvals: assigned to user Noor Whitlock</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Freya Marchetti</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-03 00:25</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Manage Permission Sets</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>PermSetAssign</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Permission set Quote Manager: assigned to user Noor Whitlock</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Idris Castellan</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-01 21:40</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Apex Class</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>changedApexClass</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Changed Class code: InvoiceService</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Ayla Zielinski</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-30 15:58</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Sharing Defaults</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>changedSharingDefault</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Changed Opportunity organization-wide default from Private to Public Read Only</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Viktor Hawthorne</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>ayla.zielinski@lumenvale.example.com</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-29 22:13</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Custom Metadata</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>changedCustomMetadataRecord</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Changed Discount Threshold record Strategic</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Marlow Sallow</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-29 17:06</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Customize Opportunities</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>createdCFRecordTypeLayout</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Changed page layout assignment for Opportunity Renewal</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Nikhil Pemberton</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:50</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Apex Class</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>changedApexClass</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Changed Class code: InvoiceService</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Callum Yarrow</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-28 17:00</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Customize Opportunities</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>createdCFRecordTypeLayout</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Changed page layout assignment for Opportunity Renewal</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Odette Fennimore</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:20</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Apex Class</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>changedApexClass</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Changed Class code: InvoiceService</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Callum Yarrow</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-27 18:19</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Customize Opportunities</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>createdCFRecordTypeLayout</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Changed page layout assignment for Opportunity Renewal</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Viktor Hawthorne</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-26 18:45</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Custom Objects</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>changedCFLength</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Changed field length for Invoice PO Number from 20 to 30</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Idris Castellan</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-26 18:01</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Email Administration</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>changedEmailDeliverability</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Changed email deliverability to All email</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Ayla Zielinski</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-25 18:48</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Manage Permission Sets</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>PermSetAssign</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Permission set Quote Manager: assigned to user Jun Jovanovic</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Ayla Zielinski</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:59</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Manage Users</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>createduser</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Created new user Tobias Lindqvist</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Callum Yarrow</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:28</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Custom Objects</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>changedCFLength</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Changed field length for Invoice PO Number from 20 to 30</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Viktor Hawthorne</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-24 18:15</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Manage Permission Sets</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>PermSetAssign</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Permission set Quote Manager: assigned to user Noor Whitlock</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Ayla Zielinski</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-24 18:06</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Custom Metadata</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>changedCustomMetadataRecord</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Changed Discount Threshold record Strategic</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Idris Castellan</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-24 14:59</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Email Administration</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>changedEmailDeliverability</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Changed email deliverability to All email</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Callum Yarrow</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-24 05:23</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Connected Apps</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>insertedConnectedApplication</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Installed connected app DataBridge Sync (package install)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Marlow Sallow</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" s="8" t="n">
+        <v>95</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-23 15:00</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Manage Permission Sets</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>PermSetAssign</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Permission set Quote Manager: assigned to user Noor Whitlock</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Ayla Zielinski</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:59</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Customize Opportunities</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>createdCFRecordTypeLayout</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Changed page layout assignment for Opportunity Renewal</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Nikhil Pemberton</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:35</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Manage Permission Sets</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>PermSetUnassign</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Permission set Lead Conversion: unassigned from user Mateo Varga</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Viktor Hawthorne</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-22 18:46</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Flows</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>activatedinteractiondefversion</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Activated flow version Case Triage, version 4</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Ayla Zielinski</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-22 15:30</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Company Information</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>changedOrgTimeZone</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Changed default time zone</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Freya Marchetti</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:52</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Manage Users</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>changedUserEmail</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Changed email for user Priya Raman</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Freya Marchetti</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-20 22:45</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Manage Users</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>createduser</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Created new user Priya Raman</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Nikhil Pemberton</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
